--- a/exports/NMDC_full_report.xlsx
+++ b/exports/NMDC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>3.37</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>16.9</v>
+        <v>16.25</v>
       </c>
       <c r="I2" t="n">
         <v>16.7443749845285</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3</v>
+        <v>-3.56</v>
       </c>
       <c r="L2" t="n">
-        <v>2.67</v>
+        <v>3.86</v>
       </c>
       <c r="M2" t="n">
         <v>0.57</v>
       </c>
       <c r="N2" t="n">
-        <v>2.87</v>
+        <v>4.73</v>
       </c>
       <c r="O2" t="n">
         <v>1.5</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.38541666666</v>
+        <v>44593.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>16.95</v>
+        <v>17.55</v>
       </c>
       <c r="I3" t="n">
         <v>17.15316520660527</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.31</v>
+        <v>-8</v>
       </c>
       <c r="L3" t="n">
-        <v>5.85</v>
+        <v>8.31</v>
       </c>
       <c r="M3" t="n">
         <v>1.5</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.83</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44606.55208333334</v>
+        <v>44607.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>18.4</v>
+        <v>17.7</v>
       </c>
       <c r="I4" t="n">
         <v>18.05795748622499</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>4.84</v>
+        <v>0.85</v>
       </c>
       <c r="L4" t="n">
         <v>3.7</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.73</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44620.55208333334</v>
+        <v>44622.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>17.3</v>
+        <v>18.2</v>
       </c>
       <c r="I5" t="n">
         <v>17.80636401913574</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>2.26</v>
+        <v>-2.82</v>
       </c>
       <c r="L5" t="n">
         <v>5.37</v>
@@ -726,7 +785,7 @@
         <v>3.38</v>
       </c>
       <c r="N5" t="n">
-        <v>4.62</v>
+        <v>5.78</v>
       </c>
       <c r="O5" t="n">
         <v>-1.63</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>10.54</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>20.25</v>
+        <v>19.15</v>
       </c>
       <c r="I6" t="n">
         <v>20.00023599008642</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K6" t="n">
-        <v>11.26</v>
+        <v>5.22</v>
       </c>
       <c r="L6" t="n">
         <v>4.95</v>
       </c>
       <c r="M6" t="n">
-        <v>1.85</v>
+        <v>2.47</v>
       </c>
       <c r="N6" t="n">
         <v>5.82</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44770.55208333334</v>
+        <v>44771.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>12.65</v>
+        <v>12.95</v>
       </c>
       <c r="I7" t="n">
         <v>12.8726860808774</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>94.16666666666667</v>
+        <v>95</v>
       </c>
       <c r="K7" t="n">
-        <v>33.94</v>
+        <v>32.38</v>
       </c>
       <c r="L7" t="n">
         <v>3.92</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>5.63</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44827.55208333334</v>
+        <v>44830.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>15.35</v>
+        <v>14.85</v>
       </c>
       <c r="I8" t="n">
         <v>15.00564740209904</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K8" t="n">
-        <v>18.53</v>
+        <v>14.67</v>
       </c>
       <c r="L8" t="n">
         <v>3.47</v>
@@ -897,7 +992,7 @@
         <v>3.37</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>4.23</v>
       </c>
       <c r="O8" t="n">
         <v>1.98</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>6.32</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>15.65</v>
+        <v>15.85</v>
       </c>
       <c r="I9" t="n">
         <v>15.78418909008297</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.39</v>
+        <v>-6.73</v>
       </c>
       <c r="L9" t="n">
-        <v>5.72</v>
+        <v>6.73</v>
       </c>
       <c r="M9" t="n">
         <v>2.97</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.31</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44881.55208333334</v>
+        <v>44882.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>30.15</v>
+        <v>29.85</v>
       </c>
       <c r="I10" t="n">
         <v>30.00177049316001</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K10" t="n">
-        <v>90.22</v>
+        <v>88.33</v>
       </c>
       <c r="L10" t="n">
         <v>4.42</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>6.7</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44883.55208333334</v>
+        <v>44886.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>31.2</v>
+        <v>32.4</v>
       </c>
       <c r="I11" t="n">
         <v>31.7257031361101</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.52</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>4.86</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.84</v>
+        <v>2.24</v>
       </c>
       <c r="N11" t="n">
         <v>4.87</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>34.05</v>
+        <v>33.45</v>
       </c>
       <c r="I12" t="n">
         <v>33.79243919016405</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>5.09</v>
+        <v>3.24</v>
       </c>
       <c r="L12" t="n">
         <v>2.78</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>5.8</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44921.55208333334</v>
+        <v>44922.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>32.6</v>
+        <v>33.55</v>
       </c>
       <c r="I13" t="n">
         <v>33.53900313598796</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>2.54</v>
+        <v>-0.3</v>
       </c>
       <c r="L13" t="n">
         <v>1.79</v>
       </c>
       <c r="M13" t="n">
-        <v>0.75</v>
+        <v>1.38</v>
       </c>
       <c r="N13" t="n">
         <v>3.99</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.91</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44950.55208333334</v>
+        <v>44951.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>35.05</v>
+        <v>35</v>
       </c>
       <c r="I14" t="n">
         <v>35.00255661494349</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K14" t="n">
-        <v>4.47</v>
+        <v>4.32</v>
       </c>
       <c r="L14" t="n">
         <v>1.64</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.19</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45027.38541666666</v>
+        <v>45027.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>32.45</v>
+        <v>32.95</v>
       </c>
       <c r="I15" t="n">
         <v>32.72114258877716</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>76</v>
+        <v>76.16666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>7.29</v>
+        <v>5.86</v>
       </c>
       <c r="L15" t="n">
         <v>1.43</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>5.13</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45036.55208333334</v>
+        <v>45037.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>32.6</v>
+        <v>31.65</v>
       </c>
       <c r="I16" t="n">
         <v>31.80869312024212</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.06</v>
+        <v>-3.95</v>
       </c>
       <c r="L16" t="n">
-        <v>2.58</v>
+        <v>5.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="N16" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
         <v>2.49</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.43</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45078.55208333334</v>
+        <v>45079.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>31.05</v>
+        <v>31.45</v>
       </c>
       <c r="I17" t="n">
         <v>31.2788144217028</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9</v>
+        <v>0.63</v>
       </c>
       <c r="L17" t="n">
         <v>2.69</v>
@@ -1410,7 +1613,7 @@
         <v>0.98</v>
       </c>
       <c r="N17" t="n">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="O17" t="n">
         <v>-2.15</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>3.94</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45096.38541666666</v>
+        <v>45096.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>30.95</v>
+        <v>30.8</v>
       </c>
       <c r="I18" t="n">
         <v>30.93428321516099</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.59</v>
+        <v>-2.07</v>
       </c>
       <c r="L18" t="n">
-        <v>1.75</v>
+        <v>2.23</v>
       </c>
       <c r="M18" t="n">
         <v>-0</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>3.36</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45110.38541666666</v>
+        <v>45110.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>31.1</v>
+        <v>31.25</v>
       </c>
       <c r="I19" t="n">
         <v>31.18602505953251</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.97</v>
+        <v>-1.46</v>
       </c>
       <c r="L19" t="n">
         <v>1.95</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>3.54</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45142.55208333334</v>
+        <v>45145.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>32.95</v>
+        <v>32.8</v>
       </c>
       <c r="I20" t="n">
         <v>32.82450396939303</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>32</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K20" t="n">
-        <v>5.44</v>
+        <v>4.96</v>
       </c>
       <c r="L20" t="n">
         <v>1.28</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>4.25</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45149.55208333334</v>
+        <v>45152.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>32.95</v>
+        <v>34.05</v>
       </c>
       <c r="I21" t="n">
         <v>33.56277087048595</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.46</v>
+        <v>-3.81</v>
       </c>
       <c r="L21" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="M21" t="n">
         <v>1.52</v>
       </c>
-      <c r="M21" t="n">
-        <v>0.45</v>
-      </c>
       <c r="N21" t="n">
-        <v>1.24</v>
+        <v>4.86</v>
       </c>
       <c r="O21" t="n">
         <v>-0.61</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.34</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>48.3</v>
+        <v>46.4</v>
       </c>
       <c r="I22" t="n">
         <v>47.17825122484448</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>67.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K22" t="n">
-        <v>41.85</v>
+        <v>36.27</v>
       </c>
       <c r="L22" t="n">
         <v>3.67</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>9.98</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45236.55208333334</v>
+        <v>45237.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>48.9</v>
+        <v>49.65</v>
       </c>
       <c r="I23" t="n">
         <v>49.43316570646254</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.39</v>
+        <v>-7</v>
       </c>
       <c r="L23" t="n">
-        <v>6.68</v>
+        <v>8.08</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.35</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>59.15</v>
+        <v>55.8</v>
       </c>
       <c r="I24" t="n">
         <v>56.61215315392403</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K24" t="n">
-        <v>19.13</v>
+        <v>12.39</v>
       </c>
       <c r="L24" t="n">
         <v>1.51</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>10.04</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45282.55208333334</v>
+        <v>45286.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>59.45</v>
+        <v>61.7</v>
       </c>
       <c r="I25" t="n">
         <v>61.38865594532153</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.54</v>
+        <v>-10.57</v>
       </c>
       <c r="L25" t="n">
-        <v>7.8</v>
+        <v>11.92</v>
       </c>
       <c r="M25" t="n">
         <v>1.61</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.48</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45302.38541666666</v>
+        <v>45302.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>64.59999999999999</v>
+        <v>63.85</v>
       </c>
       <c r="I26" t="n">
         <v>64.17156741104142</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7</v>
+        <v>3.48</v>
       </c>
       <c r="L26" t="n">
         <v>3.65</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>6.87</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45316.55208333334</v>
+        <v>45320.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>66.3</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>66.77877527111752</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>14</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.84</v>
+        <v>-5.17</v>
       </c>
       <c r="L27" t="n">
-        <v>4.07</v>
+        <v>6.11</v>
       </c>
       <c r="M27" t="n">
         <v>1.47</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>7.37</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45334.55208333334</v>
+        <v>45335.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>70.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="I28" t="n">
         <v>69.62797630777349</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
-        <v>4.39</v>
+        <v>2.76</v>
       </c>
       <c r="L28" t="n">
         <v>1.19</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>10.69</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45337.38541666666</v>
+        <v>45337.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>75.05</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>75.08135184302054</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.77</v>
+        <v>-8.91</v>
       </c>
       <c r="L29" t="n">
         <v>11.52</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45362.55208333334</v>
+        <v>45363.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>71.59999999999999</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="I30" t="n">
         <v>70.69763923256583</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.72</v>
+        <v>-7.43</v>
       </c>
       <c r="L30" t="n">
-        <v>7.94</v>
+        <v>8.02</v>
       </c>
       <c r="M30" t="n">
         <v>1.37</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.76</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45384.55208333334</v>
+        <v>45385.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>67.31999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="I31" t="n">
         <v>67.32030133115578</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K31" t="n">
-        <v>3.23</v>
+        <v>1.71</v>
       </c>
       <c r="L31" t="n">
         <v>3.79</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.42</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45434.55208333334</v>
+        <v>45435.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>85.65000000000001</v>
+        <v>82.94</v>
       </c>
       <c r="I32" t="n">
         <v>82.99042211880344</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K32" t="n">
-        <v>25.26</v>
+        <v>21.29</v>
       </c>
       <c r="L32" t="n">
         <v>2.62</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,25 +2696,25 @@
         <v>8.85</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>81.3</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="I33" t="n">
         <v>83.65366927937779</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K33" t="n">
-        <v>1.98</v>
+        <v>-1.29</v>
       </c>
       <c r="L33" t="n">
         <v>3.34</v>
       </c>
       <c r="M33" t="n">
-        <v>1.06</v>
+        <v>4.99</v>
       </c>
       <c r="N33" t="n">
         <v>3.79</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>7.41</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>83.95999999999999</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="I34" t="n">
         <v>78.22918358580021</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.06</v>
+        <v>-12.86</v>
       </c>
       <c r="L34" t="n">
-        <v>2.19</v>
+        <v>21.41</v>
       </c>
       <c r="M34" t="n">
-        <v>-0</v>
+        <v>0.24</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>11.43</v>
       </c>
       <c r="O34" t="n">
         <v>3.27</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>16.52</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45462.55208333334</v>
+        <v>45463.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>81.98999999999999</v>
+        <v>85.52</v>
       </c>
       <c r="I35" t="n">
         <v>84.54172516595165</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K35" t="n">
-        <v>-11.99</v>
+        <v>-16.81</v>
       </c>
       <c r="L35" t="n">
-        <v>15.68</v>
+        <v>17.72</v>
       </c>
       <c r="M35" t="n">
         <v>1.95</v>
       </c>
       <c r="N35" t="n">
-        <v>3.28</v>
+        <v>4.31</v>
       </c>
       <c r="O35" t="n">
         <v>-11.43</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>9.67</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45468.55208333334</v>
+        <v>45469.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>80.69</v>
+        <v>78</v>
       </c>
       <c r="I36" t="n">
         <v>79.23050517028449</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K36" t="n">
-        <v>-5.65</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>6.55</v>
+        <v>8.85</v>
       </c>
       <c r="M36" t="n">
-        <v>0.57</v>
+        <v>0.83</v>
       </c>
       <c r="N36" t="n">
-        <v>2.62</v>
+        <v>3.36</v>
       </c>
       <c r="O36" t="n">
         <v>4.31</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.73</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45499.55208333334</v>
+        <v>45502.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>74.39</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="I37" t="n">
         <v>76.37179669305264</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K37" t="n">
-        <v>4.63</v>
+        <v>1.97</v>
       </c>
       <c r="L37" t="n">
         <v>2.63</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>7.72</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>73.8</v>
+        <v>70.61</v>
       </c>
       <c r="I38" t="n">
         <v>72.16389543296441</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.48</v>
+        <v>-7.65</v>
       </c>
       <c r="L38" t="n">
-        <v>4.08</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>1.28</v>
+        <v>2.14</v>
       </c>
       <c r="N38" t="n">
-        <v>2.83</v>
+        <v>5.08</v>
       </c>
       <c r="O38" t="n">
         <v>2.69</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45547.55208333334</v>
+        <v>45548.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>67.54000000000001</v>
+        <v>69.16</v>
       </c>
       <c r="I39" t="n">
         <v>68.11521054907691</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K39" t="n">
-        <v>4.35</v>
+        <v>2.05</v>
       </c>
       <c r="L39" t="n">
         <v>4.05</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>6.62</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45553.55208333334</v>
+        <v>45554.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>66.41</v>
+        <v>65.3</v>
       </c>
       <c r="I40" t="n">
         <v>65.77031362287556</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.98</v>
+        <v>-5.58</v>
       </c>
       <c r="L40" t="n">
-        <v>5.29</v>
+        <v>7.01</v>
       </c>
       <c r="M40" t="n">
         <v>0.47</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>7.03</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45558.55208333334</v>
+        <v>45559.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>67.54000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="I41" t="n">
         <v>69.8884774379454</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.43</v>
+        <v>-7.5</v>
       </c>
       <c r="L41" t="n">
-        <v>4.53</v>
+        <v>8.06</v>
       </c>
       <c r="M41" t="n">
-        <v>0.14</v>
+        <v>1.35</v>
       </c>
       <c r="N41" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="O41" t="n">
         <v>0.77</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.29</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>74.2</v>
+        <v>71.48</v>
       </c>
       <c r="I42" t="n">
         <v>71.63678136550062</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K42" t="n">
-        <v>5.7</v>
+        <v>1.82</v>
       </c>
       <c r="L42" t="n">
         <v>2.88</v>
@@ -2835,7 +3338,7 @@
         <v>2.39</v>
       </c>
       <c r="N42" t="n">
-        <v>2.03</v>
+        <v>3.5</v>
       </c>
       <c r="O42" t="n">
         <v>3.75</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.83</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45601.38541666666</v>
+        <v>45601.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>72.52</v>
+        <v>73.33</v>
       </c>
       <c r="I43" t="n">
         <v>72.54556911336648</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.45</v>
+        <v>-2.59</v>
       </c>
       <c r="L43" t="n">
         <v>5.74</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>7.14</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>70.08</v>
+        <v>69.58</v>
       </c>
       <c r="I44" t="n">
         <v>70.05605528831835</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.43</v>
+        <v>-5.11</v>
       </c>
       <c r="L44" t="n">
-        <v>4.99</v>
+        <v>5.66</v>
       </c>
       <c r="M44" t="n">
         <v>0.64</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45631.55208333334</v>
+        <v>45632.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>73.56</v>
+        <v>74.41</v>
       </c>
       <c r="I45" t="n">
         <v>73.96666806085121</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.72</v>
+        <v>-6.94</v>
       </c>
       <c r="L45" t="n">
-        <v>6.51</v>
+        <v>7.29</v>
       </c>
       <c r="M45" t="n">
         <v>1.88</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>4.72</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45638.55208333334</v>
+        <v>45639.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>75.20999999999999</v>
+        <v>73</v>
       </c>
       <c r="I46" t="n">
         <v>73.20678585676252</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>1.08</v>
+        <v>-1.89</v>
       </c>
       <c r="L46" t="n">
-        <v>1.48</v>
+        <v>3.68</v>
       </c>
       <c r="M46" t="n">
-        <v>0.03</v>
+        <v>1.46</v>
       </c>
       <c r="N46" t="n">
-        <v>1.3</v>
+        <v>2.82</v>
       </c>
       <c r="O46" t="n">
         <v>1.69</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>5.58</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>59.4</v>
+        <v>61.42</v>
       </c>
       <c r="I47" t="n">
         <v>60.59409198528441</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K47" t="n">
-        <v>18.63</v>
+        <v>15.86</v>
       </c>
       <c r="L47" t="n">
         <v>2.15</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>8.25</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45689.55208333334</v>
+        <v>45691.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>60.33</v>
+        <v>58.3</v>
       </c>
       <c r="I48" t="n">
         <v>59.00811603799962</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.77</v>
+        <v>-5.08</v>
       </c>
       <c r="L48" t="n">
-        <v>3.91</v>
+        <v>7.42</v>
       </c>
       <c r="M48" t="n">
-        <v>1.29</v>
+        <v>1.71</v>
       </c>
       <c r="N48" t="n">
         <v>3.97</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>60.98</v>
+        <v>62.75</v>
       </c>
       <c r="I49" t="n">
         <v>62.27112659171768</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.6</v>
+        <v>-7.63</v>
       </c>
       <c r="L49" t="n">
         <v>8.109999999999999</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45715.55208333334</v>
+        <v>45716.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>60.99</v>
+        <v>58.32</v>
       </c>
       <c r="I50" t="n">
         <v>58.60771082607619</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.8</v>
+        <v>-7.06</v>
       </c>
       <c r="L50" t="n">
-        <v>4.18</v>
+        <v>7.55</v>
       </c>
       <c r="M50" t="n">
-        <v>0.62</v>
+        <v>1.1</v>
       </c>
       <c r="N50" t="n">
-        <v>2.18</v>
+        <v>3.64</v>
       </c>
       <c r="O50" t="n">
         <v>3.21</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,25 +3938,25 @@
         <v>9.27</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>61.36</v>
+        <v>63.27</v>
       </c>
       <c r="I51" t="n">
         <v>62.65779292231242</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.21</v>
+        <v>-8.49</v>
       </c>
       <c r="L51" t="n">
-        <v>5.52</v>
+        <v>8.69</v>
       </c>
       <c r="M51" t="n">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="N51" t="n">
         <v>5.21</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>68.47</v>
+        <v>63.76</v>
       </c>
       <c r="I52" t="n">
         <v>64.26467421852138</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K52" t="n">
-        <v>8.220000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="L52" t="n">
         <v>6.21</v>
@@ -3405,7 +4028,7 @@
         <v>1.37</v>
       </c>
       <c r="N52" t="n">
-        <v>1.95</v>
+        <v>7.24</v>
       </c>
       <c r="O52" t="n">
         <v>1.97</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>11.1</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>64</v>
+        <v>65.8</v>
       </c>
       <c r="I53" t="n">
         <v>64.7177016452713</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.38</v>
+        <v>-3.2</v>
       </c>
       <c r="L53" t="n">
         <v>6.59</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45783.38541666666</v>
+        <v>45783.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>63.17</v>
+        <v>62.4</v>
       </c>
       <c r="I54" t="n">
         <v>62.49234685912491</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-4</v>
+        <v>-5.17</v>
       </c>
       <c r="L54" t="n">
-        <v>5.17</v>
+        <v>5.46</v>
       </c>
       <c r="M54" t="n">
         <v>0.75</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>6.59</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45789.38541666666</v>
+        <v>45789.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>65.77</v>
+        <v>66.09</v>
       </c>
       <c r="I55" t="n">
         <v>65.90283347585012</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.4</v>
+        <v>-5.91</v>
       </c>
       <c r="L55" t="n">
-        <v>5.88</v>
+        <v>6.07</v>
       </c>
       <c r="M55" t="n">
         <v>4.28</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>7</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>70.15000000000001</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="I56" t="n">
         <v>69.10895146581854</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>6.14</v>
+        <v>3.12</v>
       </c>
       <c r="L56" t="n">
         <v>1.53</v>
       </c>
       <c r="M56" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="N56" t="n">
         <v>2.84</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.09</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45855.55208333334</v>
+        <v>45856.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>67.43000000000001</v>
+        <v>68.73</v>
       </c>
       <c r="I57" t="n">
         <v>68.45189538754477</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K57" t="n">
-        <v>1.06</v>
+        <v>-0.85</v>
       </c>
       <c r="L57" t="n">
         <v>3.14</v>
@@ -3690,7 +4373,7 @@
         <v>1.65</v>
       </c>
       <c r="N57" t="n">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="O57" t="n">
         <v>-2.47</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>4.73</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45882.55208333334</v>
+        <v>45883.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>70.5</v>
+        <v>67.27</v>
       </c>
       <c r="I58" t="n">
         <v>68.02274359181138</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K58" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="L58" t="n">
         <v>2.58</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1.59</v>
       </c>
       <c r="M58" t="n">
         <v>1.16</v>
       </c>
       <c r="N58" t="n">
-        <v>1.82</v>
+        <v>4.4</v>
       </c>
       <c r="O58" t="n">
         <v>2.55</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.67</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45901.55208333334</v>
+        <v>45902.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>67.55</v>
+        <v>70.14</v>
       </c>
       <c r="I59" t="n">
         <v>69.38918575676767</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.42</v>
+        <v>-4.27</v>
       </c>
       <c r="L59" t="n">
         <v>4.91</v>
@@ -3804,7 +4511,7 @@
         <v>1.11</v>
       </c>
       <c r="N59" t="n">
-        <v>1.58</v>
+        <v>4.84</v>
       </c>
       <c r="O59" t="n">
         <v>-4.4</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.84</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45926.38541666666</v>
+        <v>45926.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>73.79000000000001</v>
+        <v>72.84</v>
       </c>
       <c r="I60" t="n">
         <v>72.87273363905665</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="L60" t="n">
         <v>3.44</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>4.92</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45939.38541666666</v>
+        <v>45939.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>75.76000000000001</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="I61" t="n">
         <v>76.11837619141349</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.01</v>
+        <v>-5.01</v>
       </c>
       <c r="L61" t="n">
         <v>5.57</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>5.22</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45951.57291666666</v>
+        <v>45953.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>73.45999999999999</v>
+        <v>72.11</v>
       </c>
       <c r="I62" t="n">
         <v>72.49708030801581</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>12.02083333333333</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.96</v>
+        <v>-5.73</v>
       </c>
       <c r="L62" t="n">
-        <v>5.57</v>
+        <v>7.53</v>
       </c>
       <c r="M62" t="n">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
       <c r="N62" t="n">
         <v>2.16</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>4.58</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>73.70999999999999</v>
+        <v>74.45</v>
       </c>
       <c r="I63" t="n">
         <v>73.94121121903356</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.22</v>
+        <v>-3.25</v>
       </c>
       <c r="L63" t="n">
         <v>4.51</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>4.46</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45980.55208333334</v>
+        <v>45981.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>73.05</v>
+        <v>71.87</v>
       </c>
       <c r="I64" t="n">
         <v>72.17548728668473</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.88</v>
+        <v>-3.47</v>
       </c>
       <c r="L64" t="n">
-        <v>2.32</v>
+        <v>3.65</v>
       </c>
       <c r="M64" t="n">
         <v>0.27</v>
       </c>
       <c r="N64" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="O64" t="n">
         <v>1.38</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>4.9</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45992.38541666666</v>
+        <v>45992.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>73.05</v>
+        <v>73.23</v>
       </c>
       <c r="I65" t="n">
         <v>73.16787129970623</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.64</v>
+        <v>-1.89</v>
       </c>
       <c r="L65" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="M65" t="n">
         <v>1.52</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>4.26</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46030.38541666666</v>
+        <v>46030.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>80.33</v>
+        <v>79.11</v>
       </c>
       <c r="I66" t="n">
         <v>79.68013039513302</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>37.83333333333334</v>
+        <v>38</v>
       </c>
       <c r="K66" t="n">
-        <v>9.699999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L66" t="n">
         <v>2.96</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.59</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46050.38541666666</v>
+        <v>46050.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>78.76000000000001</v>
+        <v>79.19</v>
       </c>
       <c r="I67" t="n">
         <v>79.00529380080647</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K67" t="n">
-        <v>0.44</v>
+        <v>-0.1</v>
       </c>
       <c r="L67" t="n">
         <v>3.22</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.62</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>81.29000000000001</v>
+        <v>77</v>
       </c>
       <c r="I68" t="n">
         <v>78.15146961361359</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>33</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K68" t="n">
-        <v>2.65</v>
+        <v>-2.77</v>
       </c>
       <c r="L68" t="n">
         <v>3.89</v>
@@ -4317,7 +5132,7 @@
         <v>3.02</v>
       </c>
       <c r="N68" t="n">
-        <v>4.15</v>
+        <v>5.89</v>
       </c>
       <c r="O68" t="n">
         <v>2.9</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46114.55208333334</v>
+        <v>46118.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>77.90000000000001</v>
+        <v>81.77</v>
       </c>
       <c r="I69" t="n">
         <v>81.04743078296684</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.17</v>
+        <v>-6.19</v>
       </c>
       <c r="L69" t="n">
-        <v>6.38</v>
+        <v>6.87</v>
       </c>
       <c r="M69" t="n">
         <v>3.29</v>
       </c>
       <c r="N69" t="n">
-        <v>2.67</v>
+        <v>4.74</v>
       </c>
       <c r="O69" t="n">
         <v>-5.89</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>9.67</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46153.38541666666</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>87.56</v>
+        <v>86.95</v>
       </c>
       <c r="I70" t="n">
         <v>87.10072287235184</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K70" t="n">
-        <v>7.08</v>
+        <v>6.33</v>
       </c>
       <c r="L70" t="n">
         <v>4.59</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>4.95</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46154.55208333334</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>86.83</v>
+        <v>91.39</v>
       </c>
       <c r="I71" t="n">
         <v>91.18483260354461</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K71" t="n">
-        <v>0.14</v>
+        <v>-5.11</v>
       </c>
       <c r="L71" t="n">
-        <v>1.75</v>
+        <v>5.12</v>
       </c>
       <c r="M71" t="n">
         <v>0.01</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="O71" t="n">
         <v>-2.03</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>8.5</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46161.55208333334</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>88.84</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="I72" t="n">
         <v>88.19039182881438</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K72" t="n">
-        <v>-2.79</v>
+        <v>-4.27</v>
       </c>
       <c r="L72" t="n">
         <v>5.44</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>6.06</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46169.38541666666</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="H73" t="n">
-        <v>92.09</v>
+        <v>92.39</v>
       </c>
       <c r="I73" t="n">
         <v>92.24564571663146</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K73" t="n">
-        <v>-5.26</v>
+        <v>-5.6</v>
       </c>
       <c r="L73" t="n">
         <v>6.05</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>4.84</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46181.38541666666</v>
+        <v>46181.55208333334</v>
       </c>
       <c r="H74" t="n">
-        <v>90.88</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="I74" t="n">
         <v>89.61178479696973</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K74" t="n">
-        <v>-1.63</v>
+        <v>-3.41</v>
       </c>
       <c r="L74" t="n">
         <v>5.41</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>8.18</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>84.06</v>
+        <v>86.14</v>
       </c>
       <c r="I75" t="n">
         <v>85.74055470274773</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>50</v>
+        <v>50.83333333333334</v>
       </c>
       <c r="K75" t="n">
-        <v>5.8</v>
+        <v>3.47</v>
       </c>
       <c r="L75" t="n">
         <v>3.06</v>
@@ -4716,7 +5615,7 @@
         <v>1.41</v>
       </c>
       <c r="N75" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="O75" t="n">
         <v>-3.78</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>5.36</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46269.55208333334</v>
+        <v>46272.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>84.69</v>
+        <v>83.97</v>
       </c>
       <c r="I76" t="n">
         <v>84.07665974622545</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K76" t="n">
-        <v>-1.68</v>
+        <v>-2.52</v>
       </c>
       <c r="L76" t="n">
         <v>5.91</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,14 @@
       <c r="Q77" t="n">
         <v>68</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6935,7 +7866,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.5</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="6">
@@ -6945,7 +7876,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -6955,7 +7886,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>94.2</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -6965,7 +7896,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6975,7 +7906,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -6985,7 +7916,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42.3</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="11">
@@ -6995,7 +7926,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
@@ -7005,7 +7936,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -7015,7 +7946,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>73.3</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="14">
@@ -7025,7 +7956,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.11</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="15">
@@ -7035,7 +7966,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.27</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="16">
@@ -7045,7 +7976,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.13</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="17">
@@ -7055,7 +7986,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>90.22</v>
+        <v>88.33</v>
       </c>
     </row>
     <row r="18">
@@ -7065,7 +7996,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="19">
@@ -7075,7 +8006,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.26</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="20">
@@ -7085,7 +8016,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.92</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="21">
@@ -7095,7 +8026,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.68</v>
+        <v>21.41</v>
       </c>
     </row>
     <row r="22">
@@ -7105,7 +8036,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -7115,7 +8046,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -7125,7 +8056,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="25">
@@ -7145,7 +8076,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.29</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="27">
@@ -7155,7 +8086,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.91</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="28">
@@ -7165,7 +8096,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
